--- a/data-raw/Manuscript_Generic_Example.xlsx
+++ b/data-raw/Manuscript_Generic_Example.xlsx
@@ -635,22 +635,22 @@
     <t>Drug D</t>
   </si>
   <si>
-    <t>Benefit 1</t>
-  </si>
-  <si>
-    <t>Benefit 2</t>
-  </si>
-  <si>
-    <t>Benefit 3</t>
-  </si>
-  <si>
-    <t>Risk 1</t>
-  </si>
-  <si>
-    <t>Risk 2</t>
-  </si>
-  <si>
-    <t>Risk 3</t>
+    <t>Primary Efficacy</t>
+  </si>
+  <si>
+    <t>Secondary Efficacy</t>
+  </si>
+  <si>
+    <t>Quality of Life</t>
+  </si>
+  <si>
+    <t>Recurring AE</t>
+  </si>
+  <si>
+    <t>Rare SAE</t>
+  </si>
+  <si>
+    <t>Liver Toxicity</t>
   </si>
 </sst>
 </file>
@@ -2253,7 +2253,7 @@
         <v>175</v>
       </c>
       <c r="C13" s="30" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D13" s="30" t="s">
         <v>178</v>
